--- a/result/federated_learning_time.xlsx
+++ b/result/federated_learning_time.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2024mem\AI-project\FedConIoT\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3058ED55-E574-4DB1-8E15-DCE02F01C040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683FD768-D6FE-489A-8848-37B624325EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
   <si>
     <t>Device Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,14 +124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DFL Training Efficency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CFL Training Efficiency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Samples</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,6 +149,18 @@
   </si>
   <si>
     <t>learning rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFL Efficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DFL Efficency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Communication Improvement</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -163,6 +168,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -230,7 +238,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -250,6 +258,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -326,7 +346,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,6 +375,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -362,6 +400,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -391,16 +438,16 @@
       <sheetName val="time_2024-06-25_16-25-03"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="52">
           <cell r="B52">
-            <v>2.6219450999999996</v>
+            <v>2.6219451</v>
           </cell>
           <cell r="C52">
-            <v>1.9992218000000006</v>
+            <v>1.9992217999999999</v>
           </cell>
           <cell r="D52">
-            <v>2.6938581399999997</v>
+            <v>2.6938581400000001</v>
           </cell>
         </row>
       </sheetData>
@@ -672,27 +719,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q24"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="1" customWidth="1"/>
     <col min="5" max="6" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.4140625" style="20" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="14.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.08203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -703,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>13</v>
@@ -717,8 +765,8 @@
       <c r="H1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>22</v>
+      <c r="I1" s="19" t="s">
+        <v>28</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>17</v>
@@ -732,21 +780,24 @@
       <c r="M1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>21</v>
+      <c r="N1" s="21" t="s">
+        <v>29</v>
       </c>
       <c r="O1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="16">
         <v>5</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="16">
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -768,7 +819,7 @@
         <f>SUM(E2:G2)</f>
         <v>30.065200279999999</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="19">
         <f t="shared" ref="I2:I11" si="0">D2*3/H2</f>
         <v>99.783137050833574</v>
       </c>
@@ -785,7 +836,7 @@
         <f>SUM(J2:L2)</f>
         <v>24.430592280000003</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="21">
         <f t="shared" ref="N2:N11" si="1">D2*3/M2</f>
         <v>122.79685918445526</v>
       </c>
@@ -793,13 +844,17 @@
         <f t="shared" ref="O2:O11" si="2">(N2-I2)/I2</f>
         <v>0.23063738837853495</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="9">
+        <f>((E2+G2)-J2-L2)/(E2+G2)</f>
+        <v>0.31694797947919179</v>
+      </c>
+      <c r="Q2" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
@@ -819,27 +874,27 @@
         <f t="shared" ref="H3:H11" si="3">SUM(E3:G3)</f>
         <v>8.7426472400000002</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="19">
         <f t="shared" si="0"/>
         <v>952.91503492024685</v>
       </c>
       <c r="J3" s="4">
         <f>'[1]time_2024-06-25_16-25-03'!B52</f>
-        <v>2.6219450999999996</v>
+        <v>2.6219451</v>
       </c>
       <c r="K3" s="4">
         <f>'[1]time_2024-06-25_16-25-03'!C52</f>
-        <v>1.9992218000000006</v>
+        <v>1.9992217999999999</v>
       </c>
       <c r="L3" s="4">
         <f>'[1]time_2024-06-25_16-25-03'!D52</f>
-        <v>2.6938581399999997</v>
+        <v>2.6938581400000001</v>
       </c>
       <c r="M3" s="8">
         <f>SUM(J3:L3)</f>
         <v>7.3150250400000001</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="21">
         <f t="shared" si="1"/>
         <v>1138.8887877272393</v>
       </c>
@@ -847,15 +902,19 @@
         <f t="shared" si="2"/>
         <v>0.19516299564163908</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="9">
+        <f t="shared" ref="P3:P11" si="4">((E3+G3)-J3-L3)/(E3+G3)</f>
+        <v>0.19345014428248364</v>
+      </c>
+      <c r="Q3" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
         <v>7</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="16">
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -877,7 +936,7 @@
         <f>SUM(E4:G4)</f>
         <v>30.729271079999997</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="19">
         <f t="shared" si="0"/>
         <v>136.67750169100336</v>
       </c>
@@ -894,7 +953,7 @@
         <f>SUM(J4:L4)</f>
         <v>26.092530559999993</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="21">
         <f t="shared" si="1"/>
         <v>160.96560624283126</v>
       </c>
@@ -902,15 +961,19 @@
         <f t="shared" si="2"/>
         <v>0.17770374971250033</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="9">
+        <f t="shared" si="4"/>
+        <v>0.33676876171867937</v>
+      </c>
+      <c r="Q4" s="2">
         <v>1234</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2">
         <f>1620+200*4</f>
@@ -929,7 +992,7 @@
         <f t="shared" si="3"/>
         <v>29.850277900000002</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="19">
         <f t="shared" si="0"/>
         <v>243.2138161098996</v>
       </c>
@@ -946,7 +1009,7 @@
         <f>SUM(J5:L5)</f>
         <v>24.643346579999999</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="21">
         <f t="shared" si="1"/>
         <v>294.60284448103556</v>
       </c>
@@ -954,15 +1017,19 @@
         <f t="shared" si="2"/>
         <v>0.21129156720239572</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="9">
+        <f t="shared" si="4"/>
+        <v>0.39431364988404694</v>
+      </c>
+      <c r="Q5" s="2">
         <v>1234</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2">
         <f>2777+400</f>
@@ -981,7 +1048,7 @@
         <f t="shared" si="3"/>
         <v>29.612143159999995</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="19">
         <f t="shared" si="0"/>
         <v>321.8612022946873</v>
       </c>
@@ -995,10 +1062,10 @@
         <v>4.0811739000000005</v>
       </c>
       <c r="M6" s="8">
-        <f t="shared" ref="M6:M11" si="4">SUM(J6:L6)</f>
+        <f t="shared" ref="M6:M11" si="5">SUM(J6:L6)</f>
         <v>24.750563759999999</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="21">
         <f t="shared" si="1"/>
         <v>385.08213761996348</v>
       </c>
@@ -1006,15 +1073,19 @@
         <f t="shared" si="2"/>
         <v>0.19642297634678196</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="9">
+        <f t="shared" si="4"/>
+        <v>0.36142627124464533</v>
+      </c>
+      <c r="Q6" s="2">
         <v>1234</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
         <v>10</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="16">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1036,7 +1107,7 @@
         <f t="shared" si="3"/>
         <v>34.291650059999995</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="19">
         <f t="shared" si="0"/>
         <v>174.9697080630946</v>
       </c>
@@ -1050,10 +1121,10 @@
         <v>6.2445531400000007</v>
       </c>
       <c r="M7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>29.204541120000002</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="21">
         <f t="shared" si="1"/>
         <v>205.44750130968671</v>
       </c>
@@ -1061,13 +1132,17 @@
         <f t="shared" si="2"/>
         <v>0.17418897010219467</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="9">
+        <f t="shared" si="4"/>
+        <v>0.30518658030540041</v>
+      </c>
+      <c r="Q7" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
@@ -1087,7 +1162,7 @@
         <f t="shared" si="3"/>
         <v>34.180522119999999</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="19">
         <f t="shared" si="0"/>
         <v>331.50459083742049</v>
       </c>
@@ -1101,10 +1176,10 @@
         <v>5.5986875600000001</v>
       </c>
       <c r="M8" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>27.226631519999998</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="21">
         <f t="shared" si="1"/>
         <v>416.1734069701767</v>
       </c>
@@ -1112,15 +1187,19 @@
         <f t="shared" si="2"/>
         <v>0.25540767299443001</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="9">
+        <f t="shared" si="4"/>
+        <v>0.39779455243998524</v>
+      </c>
+      <c r="Q8" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
         <v>13</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="16">
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1142,7 +1221,7 @@
         <f t="shared" si="3"/>
         <v>39.302076239999998</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="19">
         <f t="shared" si="0"/>
         <v>334.10448648603</v>
       </c>
@@ -1156,10 +1235,10 @@
         <v>6.5970377599999992</v>
       </c>
       <c r="M9" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>29.422145979999993</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="21">
         <f t="shared" si="1"/>
         <v>446.29647371493337</v>
       </c>
@@ -1167,13 +1246,17 @@
         <f t="shared" si="2"/>
         <v>0.33579910407337343</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="9">
+        <f t="shared" si="4"/>
+        <v>0.43693449810053403</v>
+      </c>
+      <c r="Q9" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1193,7 +1276,7 @@
         <f t="shared" si="3"/>
         <v>39.202588740000003</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="19">
         <f t="shared" si="0"/>
         <v>277.02252195705375</v>
       </c>
@@ -1207,10 +1290,10 @@
         <v>6.8621308399999998</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>30.063691180000003</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10" s="21">
         <f t="shared" si="1"/>
         <v>361.23308794578958</v>
       </c>
@@ -1218,11 +1301,15 @@
         <f t="shared" si="2"/>
         <v>0.30398454751556558</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="9">
+        <f t="shared" si="4"/>
+        <v>0.41142888445308573</v>
+      </c>
+      <c r="Q10" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>15</v>
       </c>
@@ -1233,7 +1320,7 @@
         <v>12</v>
       </c>
       <c r="D11" s="2">
-        <v>3777</v>
+        <v>4777</v>
       </c>
       <c r="E11" s="3">
         <v>11.28022502</v>
@@ -1248,9 +1335,9 @@
         <f t="shared" si="3"/>
         <v>44.290734839999999</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="19">
         <f t="shared" si="0"/>
-        <v>255.83228729288791</v>
+        <v>323.56654392325277</v>
       </c>
       <c r="J11" s="4">
         <v>6.35874424</v>
@@ -1262,48 +1349,52 @@
         <v>7.8152010799999996</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>31.223798160000001</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="21">
         <f t="shared" si="1"/>
-        <v>362.89627360312141</v>
+        <v>458.97683320151208</v>
       </c>
       <c r="O11" s="9">
         <f t="shared" si="2"/>
-        <v>0.41849286281704545</v>
-      </c>
-      <c r="P11" s="2">
+        <v>0.4184928628170454</v>
+      </c>
+      <c r="P11" s="9">
+        <f t="shared" si="4"/>
+        <v>0.44899353947214266</v>
+      </c>
+      <c r="Q11" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B22" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23" s="6">
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B24" s="6">
         <v>1E-3</v>
@@ -1324,4 +1415,885 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B531A075-0FD0-4E05-BE21-45071FA4AF7B}">
+  <dimension ref="A1:Q24"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.4140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.4140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="16">
+        <v>5</v>
+      </c>
+      <c r="B2" s="16">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3.7201091899999987</v>
+      </c>
+      <c r="F2" s="3">
+        <v>16.723166970000005</v>
+      </c>
+      <c r="G2" s="3">
+        <v>4.9654514399999998</v>
+      </c>
+      <c r="H2" s="7">
+        <f>SUM(E2:G2)</f>
+        <v>25.408727600000002</v>
+      </c>
+      <c r="I2" s="3">
+        <f>D2/H2*3</f>
+        <v>118.06966673923489</v>
+      </c>
+      <c r="J2" s="4">
+        <v>3.0769838900000002</v>
+      </c>
+      <c r="K2" s="4">
+        <v>16.754388550000002</v>
+      </c>
+      <c r="L2" s="5">
+        <v>3.79303598</v>
+      </c>
+      <c r="M2" s="8">
+        <f>SUM(J2:L2)</f>
+        <v>23.624408420000002</v>
+      </c>
+      <c r="N2" s="4">
+        <f>D2/M2*3</f>
+        <v>126.98730680004047</v>
+      </c>
+      <c r="O2" s="11">
+        <f>(H2-M2)/H2</f>
+        <v>7.022465697967499E-2</v>
+      </c>
+      <c r="P2" s="9">
+        <f>((E2+G2)-(J2+L2))/(E2+G2)</f>
+        <v>0.20902977220941904</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2777</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4.0349758600000003</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.1445507199999998</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4.9210100800000003</v>
+      </c>
+      <c r="H3" s="7">
+        <f>SUM(E3:G3)</f>
+        <v>11.10053666</v>
+      </c>
+      <c r="I3" s="3">
+        <f>D3/H3*3</f>
+        <v>750.50425535011937</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2.7700429000000009</v>
+      </c>
+      <c r="K3" s="4">
+        <v>2.0146998100000006</v>
+      </c>
+      <c r="L3" s="4">
+        <v>2.7884799699999996</v>
+      </c>
+      <c r="M3" s="8">
+        <f>SUM(J3:L3)</f>
+        <v>7.5732226800000007</v>
+      </c>
+      <c r="N3" s="4">
+        <f>D3/M3*3</f>
+        <v>1100.0600869694749</v>
+      </c>
+      <c r="O3" s="15">
+        <f>(H3-M3)/H3</f>
+        <v>0.31776067122145779</v>
+      </c>
+      <c r="P3" s="9">
+        <f>((E3+G3)-(J3+L3))/(E3+G3)</f>
+        <v>0.37935109464899408</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
+        <v>7</v>
+      </c>
+      <c r="B4" s="16">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1400</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5.2874820899999975</v>
+      </c>
+      <c r="F4" s="3">
+        <v>16.917219119999999</v>
+      </c>
+      <c r="G4" s="3">
+        <v>7.2364098000000006</v>
+      </c>
+      <c r="H4" s="7">
+        <f>SUM(E4:G4)</f>
+        <v>29.441111009999997</v>
+      </c>
+      <c r="I4" s="3">
+        <f>D4/H4*3</f>
+        <v>142.65765984759963</v>
+      </c>
+      <c r="J4" s="4">
+        <v>5.2031430299999997</v>
+      </c>
+      <c r="K4" s="4">
+        <v>17.068447280000001</v>
+      </c>
+      <c r="L4" s="4">
+        <v>5.7750582799999997</v>
+      </c>
+      <c r="M4" s="8">
+        <f>SUM(J4:L4)</f>
+        <v>28.04664859</v>
+      </c>
+      <c r="N4" s="4">
+        <f>D4/M4*3</f>
+        <v>149.75051249073323</v>
+      </c>
+      <c r="O4" s="11">
+        <f>(H4-M4)/H4</f>
+        <v>4.7364463233957169E-2</v>
+      </c>
+      <c r="P4" s="9">
+        <f>((E4+G4)-(J4+L4))/(E4+G4)</f>
+        <v>0.12341934867979756</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2">
+        <f>1620+200*4</f>
+        <v>2420</v>
+      </c>
+      <c r="E5" s="3">
+        <v>6.33050289</v>
+      </c>
+      <c r="F5" s="3">
+        <v>17.339979500000002</v>
+      </c>
+      <c r="G5" s="3">
+        <v>7.6971484299999977</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" ref="H5:H11" si="0">SUM(E5:G5)</f>
+        <v>31.367630820000002</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" ref="I5:I11" si="1">D5/H5*3</f>
+        <v>231.44878367323247</v>
+      </c>
+      <c r="J5" s="4">
+        <v>4.6410016600000006</v>
+      </c>
+      <c r="K5" s="4">
+        <v>17.025515929999994</v>
+      </c>
+      <c r="L5" s="4">
+        <v>6.9719197700000066</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" ref="M5:M11" si="2">SUM(J5:L5)</f>
+        <v>28.638437360000001</v>
+      </c>
+      <c r="N5" s="4">
+        <f t="shared" ref="N5:N11" si="3">D5/M5*3</f>
+        <v>253.50545173739886</v>
+      </c>
+      <c r="O5" s="15">
+        <f t="shared" ref="O5:O11" si="4">(H5-M5)/H5</f>
+        <v>8.7006681367209515E-2</v>
+      </c>
+      <c r="P5" s="9">
+        <f t="shared" ref="P5:P11" si="5">((E5+G5)-(J5+L5))/(E5+G5)</f>
+        <v>0.17214071229138522</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2">
+        <f>2777+400</f>
+        <v>3177</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O6" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P6" s="9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16">
+        <v>3</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8.4085967600000018</v>
+      </c>
+      <c r="F7" s="3">
+        <v>17.322554319999998</v>
+      </c>
+      <c r="G7" s="3">
+        <v>11.143573179999997</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="0"/>
+        <v>36.874724259999994</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="1"/>
+        <v>162.71308112555906</v>
+      </c>
+      <c r="J7" s="4">
+        <v>7.7863977999999952</v>
+      </c>
+      <c r="K7" s="4">
+        <v>17.128525539999995</v>
+      </c>
+      <c r="L7" s="4">
+        <v>8.3197631200000011</v>
+      </c>
+      <c r="M7" s="8">
+        <f t="shared" si="2"/>
+        <v>33.234686459999992</v>
+      </c>
+      <c r="N7" s="4">
+        <f t="shared" si="3"/>
+        <v>180.53427425052956</v>
+      </c>
+      <c r="O7" s="15">
+        <f t="shared" si="4"/>
+        <v>9.8713627641916976E-2</v>
+      </c>
+      <c r="P7" s="9">
+        <f t="shared" si="5"/>
+        <v>0.17624688362339397</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3777</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O8" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P8" s="9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
+        <v>13</v>
+      </c>
+      <c r="B9" s="16">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4377</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O9" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P9" s="9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3620</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P10" s="9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2">
+        <v>4</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4777</v>
+      </c>
+      <c r="E11" s="3">
+        <v>12.684124749999999</v>
+      </c>
+      <c r="F11" s="3">
+        <v>18.113951989999997</v>
+      </c>
+      <c r="G11" s="3">
+        <v>15.875582239999998</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="0"/>
+        <v>46.673658979999992</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="1"/>
+        <v>307.04685069025635</v>
+      </c>
+      <c r="J11" s="4">
+        <v>6.7327718400000034</v>
+      </c>
+      <c r="K11" s="4">
+        <v>17.329878260000001</v>
+      </c>
+      <c r="L11" s="4">
+        <v>9.1737566400000006</v>
+      </c>
+      <c r="M11" s="8">
+        <f t="shared" si="2"/>
+        <v>33.236406740000007</v>
+      </c>
+      <c r="N11" s="4">
+        <f t="shared" si="3"/>
+        <v>431.1837952913437</v>
+      </c>
+      <c r="O11" s="15">
+        <f t="shared" si="4"/>
+        <v>0.28789798215215884</v>
+      </c>
+      <c r="P11" s="9">
+        <f t="shared" si="5"/>
+        <v>0.44304300861456397</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="6">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="6">
+        <v>50</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="6">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>